--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/exportDiscloseRecord12.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/exportDiscloseRecord12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinhaochen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kf-project\hhwy_szjt\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ECD4E6-3A8D-42B2-BE53-ABFB0D71AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B09228-0305-447A-99F3-C256C225E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,12 +132,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +470,7 @@
     <col min="6" max="6" width="16.77734375" customWidth="1"/>
     <col min="7" max="7" width="12.109375" customWidth="1"/>
     <col min="8" max="8" width="12.109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -493,7 +499,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/exportDiscloseRecord12.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/exportDiscloseRecord12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kf-project\hhwy_szjt\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\company2024\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B09228-0305-447A-99F3-C256C225E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EDAFB8-399A-4E6E-B859-30150A45982C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>交底等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,6 +59,14 @@
   </si>
   <si>
     <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交底编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,50 +467,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="16.125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="12.125" customWidth="1"/>
+    <col min="9" max="9" width="12.125" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="14.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
